--- a/assets/data/sinners.xlsx
+++ b/assets/data/sinners.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="330">
   <si>
     <t>FactionName</t>
   </si>
@@ -50,52 +50,58 @@
     <t>Sinner</t>
   </si>
   <si>
+    <t>ID Name</t>
+  </si>
+  <si>
     <t>hasYiSang</t>
   </si>
   <si>
+    <t>Stars</t>
+  </si>
+  <si>
     <t>hasFaust</t>
   </si>
   <si>
-    <t>ID Name</t>
-  </si>
-  <si>
     <t>hasDonQuixote</t>
   </si>
   <si>
-    <t>Stars</t>
-  </si>
-  <si>
     <t>hasRyoshu</t>
   </si>
   <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>hasMeursault</t>
   </si>
   <si>
-    <t>Level</t>
+    <t>Faction</t>
   </si>
   <si>
     <t>hasHongLu</t>
   </si>
   <si>
+    <t>Season</t>
+  </si>
+  <si>
     <t>hasHeathcliff</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>hasIshmael</t>
   </si>
   <si>
-    <t>Faction</t>
-  </si>
-  <si>
     <t>hasRodion</t>
   </si>
   <si>
+    <t>Difficulty</t>
+  </si>
+  <si>
     <t>hasSinclair</t>
   </si>
   <si>
-    <t>Season</t>
+    <t>Available</t>
   </si>
   <si>
     <t>hasOutis</t>
@@ -104,597 +110,591 @@
     <t>hasGregor</t>
   </si>
   <si>
-    <t>Difficulty</t>
-  </si>
-  <si>
     <t>factionDifficulty</t>
   </si>
   <si>
-    <t>Available</t>
-  </si>
-  <si>
     <t>levelled</t>
   </si>
   <si>
+    <t>LCB Sinner</t>
+  </si>
+  <si>
+    <t>"Sinking"</t>
+  </si>
+  <si>
     <t>Blade Lineage</t>
   </si>
   <si>
-    <t>LCB Sinner</t>
+    <t>"LCB","Limbus Company"</t>
+  </si>
+  <si>
+    <t>Blade Lineage Salsu</t>
+  </si>
+  <si>
+    <t>"Poise"</t>
+  </si>
+  <si>
+    <t>"Syndicate","Blade Lineage"</t>
   </si>
   <si>
     <t>Bloodfiends of La Mancha</t>
   </si>
   <si>
-    <t>"Sinking"</t>
-  </si>
-  <si>
-    <t>"LCB","Limbus Company"</t>
-  </si>
-  <si>
-    <t>Blade Lineage Salsu</t>
-  </si>
-  <si>
-    <t>"Poise"</t>
+    <t>Dieci Assoc. South Section 4</t>
+  </si>
+  <si>
+    <t>"Fixer","Dieci Association"</t>
+  </si>
+  <si>
+    <t>Effloresced EGO::Spicebush</t>
+  </si>
+  <si>
+    <t>"Technology Liberation Alliance"</t>
   </si>
   <si>
     <t>Cinq Association</t>
   </si>
   <si>
-    <t>"Syndicate","Blade Lineage"</t>
-  </si>
-  <si>
-    <t>Dieci Assoc. South Section 4</t>
+    <t>Heishou Pack - Wu Branch Adept</t>
+  </si>
+  <si>
+    <t>"Rupture","Tremor"</t>
+  </si>
+  <si>
+    <t>"H Corp","Heishou Pack - Wu Branch","Jia Family"</t>
+  </si>
+  <si>
+    <t>LCE E.G.O::Dimension Shredder</t>
   </si>
   <si>
     <t>Dawn Office</t>
   </si>
   <si>
-    <t>"Fixer","Dieci Association"</t>
-  </si>
-  <si>
-    <t>Effloresced EGO::Spicebush</t>
+    <t>"Charge","Rupture"</t>
+  </si>
+  <si>
+    <t>"E.G.O Gear","LCE","Limbus Company"</t>
+  </si>
+  <si>
+    <t>LCE E.G.O::Lantern</t>
+  </si>
+  <si>
+    <t>"Rupture"</t>
   </si>
   <si>
     <t>Devyat Association</t>
   </si>
   <si>
-    <t>"Technology Liberation Alliance"</t>
-  </si>
-  <si>
-    <t>Heishou Pack - Wu Branch Adept</t>
-  </si>
-  <si>
-    <t>"Rupture","Tremor"</t>
-  </si>
-  <si>
-    <t>"H Corp","Heishou Pack - Wu Branch","Jia Family"</t>
+    <t>Liu Assoc. South Section 3</t>
+  </si>
+  <si>
+    <t>"Burn"</t>
+  </si>
+  <si>
+    <t>"Fixer","Liu Association"</t>
   </si>
   <si>
     <t>Dieci Association</t>
   </si>
   <si>
-    <t>LCE E.G.O::Dimension Shredder</t>
-  </si>
-  <si>
-    <t>"Charge","Rupture"</t>
-  </si>
-  <si>
-    <t>"E.G.O Gear","LCE","Limbus Company"</t>
+    <t>Lobotomy E.G.O::Solemn Lament</t>
+  </si>
+  <si>
+    <t>"E.G.O Gear","Lobotomy Corp. Headquarters"</t>
   </si>
   <si>
     <t>Fanghunt Office</t>
   </si>
   <si>
-    <t>LCE E.G.O::Lantern</t>
-  </si>
-  <si>
-    <t>"Rupture"</t>
+    <t>Molar Office Fixer</t>
+  </si>
+  <si>
+    <t>"Tremor"</t>
+  </si>
+  <si>
+    <t>"Fixer","Molar Office"</t>
   </si>
   <si>
     <t>Firefist Office</t>
   </si>
   <si>
-    <t>Liu Assoc. South Section 3</t>
-  </si>
-  <si>
-    <t>"Burn"</t>
-  </si>
-  <si>
-    <t>"Fixer","Liu Association"</t>
+    <t>N Corp. E.G.O::Fell Bullet</t>
+  </si>
+  <si>
+    <t>"Poise","Bleed"</t>
+  </si>
+  <si>
+    <t>"E.G.O Gear","N Corp."</t>
+  </si>
+  <si>
+    <t>Seven Assoc. South Section 6</t>
   </si>
   <si>
     <t>Full-Stop Office</t>
   </si>
   <si>
-    <t>Lobotomy E.G.O::Solemn Lament</t>
-  </si>
-  <si>
-    <t>"E.G.O Gear","Lobotomy Corp. Headquarters"</t>
+    <t>"Fixer","Seven Association"</t>
+  </si>
+  <si>
+    <t>The House of Spiders: The Index Nursefather</t>
+  </si>
+  <si>
+    <t>"Poise","Sinking","Burn"</t>
+  </si>
+  <si>
+    <t>"The Fingers","The House of Spiders","The Index"</t>
   </si>
   <si>
     <t>G Corp</t>
   </si>
   <si>
-    <t>Molar Office Fixer</t>
-  </si>
-  <si>
-    <t>"Tremor"</t>
-  </si>
-  <si>
-    <t>"Fixer","Molar Office"</t>
+    <t>The Pequod First Mate</t>
+  </si>
+  <si>
+    <t>"'The Pequod"</t>
+  </si>
+  <si>
+    <t>The Ring Pointillist Student</t>
   </si>
   <si>
     <t>H Corp</t>
   </si>
   <si>
-    <t>N Corp. E.G.O::Fell Bullet</t>
-  </si>
-  <si>
-    <t>"Poise","Bleed"</t>
-  </si>
-  <si>
-    <t>"E.G.O Gear","N Corp."</t>
+    <t>"Bleed"</t>
+  </si>
+  <si>
+    <t>"The Fingers","The Ring","School of Pointillism"</t>
+  </si>
+  <si>
+    <t>W Corp. L3 Cleanup Agent</t>
+  </si>
+  <si>
+    <t>"W Corp."</t>
   </si>
   <si>
     <t>Hook Office</t>
   </si>
   <si>
-    <t>Seven Assoc. South Section 6</t>
-  </si>
-  <si>
-    <t>"Fixer","Seven Association"</t>
-  </si>
-  <si>
     <t>Jeong Office</t>
   </si>
   <si>
-    <t>The House of Spiders: The Index Nursefather</t>
-  </si>
-  <si>
-    <t>"Poise","Sinking","Burn"</t>
-  </si>
-  <si>
-    <t>"The Fingers","The House of Spiders","The Index"</t>
+    <t>Dawn Office Fixer</t>
+  </si>
+  <si>
+    <t>"Burn","Tremor"</t>
+  </si>
+  <si>
+    <t>"Fixer","Dawn Office"</t>
   </si>
   <si>
     <t>K Corp</t>
   </si>
   <si>
-    <t>The Pequod First Mate</t>
-  </si>
-  <si>
-    <t>"'The Pequod"</t>
-  </si>
-  <si>
-    <t>The Ring Pointillist Student</t>
+    <t>Heishou Pack - Mao Branch Adept</t>
+  </si>
+  <si>
+    <t>"Heishou Pack","H Corp.","Heishou Pack - Mao Branch","The Pinky"</t>
   </si>
   <si>
     <t>Kurokumo Clan</t>
   </si>
   <si>
-    <t>"Bleed"</t>
-  </si>
-  <si>
-    <t>"The Fingers","The Ring","School of Pointillism"</t>
+    <t>LCE E.G.O::Ardor Blossom Star</t>
+  </si>
+  <si>
+    <t>Lobotomy Corp. Remnant</t>
+  </si>
+  <si>
+    <t>"Rupture","Poise"</t>
+  </si>
+  <si>
+    <t>"Lobotomy Corp. Branch","Fixer"</t>
   </si>
   <si>
     <t>LCA</t>
   </si>
   <si>
-    <t>W Corp. L3 Cleanup Agent</t>
-  </si>
-  <si>
-    <t>"W Corp."</t>
+    <t>Lobotomy E.G.O::Regret</t>
+  </si>
+  <si>
+    <t>MultiCrack Office Rep</t>
+  </si>
+  <si>
+    <t>"Charge"</t>
+  </si>
+  <si>
+    <t>"Mechanical Amalgam","Fixer","MultiCrack Office"</t>
+  </si>
+  <si>
+    <t>Seven Assoc. South Section 4</t>
   </si>
   <si>
     <t>LCB Top Shelf</t>
   </si>
   <si>
+    <t>Shi Assoc. East Section 3</t>
+  </si>
+  <si>
+    <t>"Fixer","Shi Association"</t>
+  </si>
+  <si>
+    <t>The House of Spiders: The Ring Apprentice</t>
+  </si>
+  <si>
     <t>LCB Bottom Shelf</t>
   </si>
   <si>
-    <t>Dawn Office Fixer</t>
-  </si>
-  <si>
-    <t>"Burn","Tremor"</t>
-  </si>
-  <si>
-    <t>"Fixer","Dawn Office"</t>
+    <t>"Bleed","Charge"</t>
+  </si>
+  <si>
+    <t>"The House of Spiders","The Ring","School of Corporism"</t>
+  </si>
+  <si>
+    <t>The Index Proselyte: [Paper Slip]</t>
+  </si>
+  <si>
+    <t>"Poise","Sinking"</t>
+  </si>
+  <si>
+    <t>"The Fingers","The Index"</t>
+  </si>
+  <si>
+    <t>The One Who Grips</t>
   </si>
   <si>
     <t>LCCB</t>
   </si>
   <si>
-    <t>Heishou Pack - Mao Branch Adept</t>
+    <t>"N Corp. Fanatic","N Corp."</t>
+  </si>
+  <si>
+    <t>W Corp. L2 Cleanup Agent</t>
   </si>
   <si>
     <t>LCD</t>
   </si>
   <si>
+    <t>Wuthering Heights Butler</t>
+  </si>
+  <si>
+    <t>"Fixer","Wuthering Heights"</t>
+  </si>
+  <si>
+    <t>Zwei Assoc. South Section 4</t>
+  </si>
+  <si>
+    <t>"Fixer","Zwei Association"</t>
+  </si>
+  <si>
     <t>LCE</t>
   </si>
   <si>
-    <t>"Heishou Pack","H Corp.","Heishou Pack - Mao Branch","The Pinky"</t>
-  </si>
-  <si>
-    <t>LCE E.G.O::Ardor Blossom Star</t>
+    <t>Cinq Assoc. East Section 3</t>
   </si>
   <si>
     <t>Library Walp</t>
   </si>
   <si>
+    <t>"Poise","Burn"</t>
+  </si>
+  <si>
+    <t>"Fixer","Cinq Association"</t>
+  </si>
+  <si>
+    <t>Cinq Assoc. South Section 5 Director</t>
+  </si>
+  <si>
     <t>Liu</t>
   </si>
   <si>
-    <t>Lobotomy Corp. Remnant</t>
-  </si>
-  <si>
-    <t>"Rupture","Poise"</t>
-  </si>
-  <si>
-    <t>"Lobotomy Corp. Branch","Fixer"</t>
+    <t>Heishou Pack - Wei Branch</t>
+  </si>
+  <si>
+    <t>"Rupture","Sinking"</t>
+  </si>
+  <si>
+    <t>"Heishou Pack","H Corp","Heishou Pack - Wei Branch"</t>
+  </si>
+  <si>
+    <t>Lobotomy E.G.O::In the Name of Love and Hate</t>
+  </si>
+  <si>
+    <t>"Rupture","Sinking","Charge"</t>
   </si>
   <si>
     <t>Lob E.G.O.</t>
   </si>
   <si>
-    <t>Lobotomy E.G.O::Regret</t>
+    <t>Lobotomy E.G.O::Lantern</t>
+  </si>
+  <si>
+    <t>'E.G.O Gear","Lobotomy Corp. Headquarters"</t>
   </si>
   <si>
     <t>Lob Remnant</t>
   </si>
   <si>
-    <t>MultiCrack Office Rep</t>
-  </si>
-  <si>
-    <t>"Charge"</t>
-  </si>
-  <si>
-    <t>"Mechanical Amalgam","Fixer","MultiCrack Office"</t>
+    <t>N Corp. Mittelhammer</t>
   </si>
   <si>
     <t>Los Mariachis</t>
   </si>
   <si>
-    <t>Seven Assoc. South Section 4</t>
+    <t>"Bleed","Tremor"</t>
+  </si>
+  <si>
+    <t>Shi Assoc. South Section 5 Director</t>
   </si>
   <si>
     <t>Molar</t>
   </si>
   <si>
-    <t>Shi Assoc. East Section 3</t>
-  </si>
-  <si>
-    <t>"Fixer","Shi Association"</t>
-  </si>
-  <si>
-    <t>The House of Spiders: The Ring Apprentice</t>
+    <t>T Corp. Class 3 Collection Staff</t>
+  </si>
+  <si>
+    <t>"T Corp."</t>
+  </si>
+  <si>
+    <t>The Index Proxy - Effloresced E.G.O::Procuration</t>
   </si>
   <si>
     <t>Multicrack Office</t>
   </si>
   <si>
-    <t>"Bleed","Charge"</t>
-  </si>
-  <si>
-    <t>"The House of Spiders","The Ring","School of Corporism"</t>
+    <t>The Manager of La Manchaland</t>
+  </si>
+  <si>
+    <t>"Second Kindred","Bloodfiend","La Manchaland"</t>
+  </si>
+  <si>
+    <t>The Middle Little Sister</t>
+  </si>
+  <si>
+    <t>"The Fingers","The Middle"</t>
   </si>
   <si>
     <t>N Corp EGO</t>
   </si>
   <si>
-    <t>The Index Proselyte: [Paper Slip]</t>
-  </si>
-  <si>
-    <t>"Poise","Sinking"</t>
-  </si>
-  <si>
-    <t>"The Fingers","The Index"</t>
+    <t>"Rupture","Charge"</t>
+  </si>
+  <si>
+    <t>"Tiansha Star","LCB","Limbus Company","The Pinky"</t>
   </si>
   <si>
     <t>N Corp Fanatics</t>
   </si>
   <si>
-    <t>The One Who Grips</t>
-  </si>
-  <si>
-    <t>"N Corp. Fanatic","N Corp."</t>
-  </si>
-  <si>
-    <t>W Corp. L2 Cleanup Agent</t>
+    <t>The Blade of the House of Spiders</t>
+  </si>
+  <si>
+    <t>"Poise","Bleed","Burn"</t>
+  </si>
+  <si>
+    <t>"The Fingers","The House of Spiders","The Pinky","Tiansha Star"</t>
   </si>
   <si>
     <t>Night Awls</t>
   </si>
   <si>
-    <t>Wuthering Heights Butler</t>
+    <t>District 20 Yurodivy</t>
   </si>
   <si>
     <t>Oufi Association</t>
   </si>
   <si>
-    <t>"Fixer","Wuthering Heights"</t>
-  </si>
-  <si>
-    <t>Zwei Assoc. South Section 4</t>
+    <t>"Syndicate","Yurodiviye"</t>
+  </si>
+  <si>
+    <t>Drifting Blade of Hongyuan</t>
   </si>
   <si>
     <t>R Corp</t>
   </si>
   <si>
-    <t>"Fixer","Zwei Association"</t>
+    <t>"H Corp."</t>
+  </si>
+  <si>
+    <t>Edgar Family Chief Butler</t>
   </si>
   <si>
     <t>R.B. Chefs</t>
   </si>
   <si>
+    <t>"Fixer","Edgar Family"</t>
+  </si>
+  <si>
+    <t>Heishou Pack - Mao Branch</t>
+  </si>
+  <si>
+    <t>"Heishou Pack","H Corp","Heishou Pack - Mao Branch"</t>
+  </si>
+  <si>
     <t>Rosespanner Workshop</t>
   </si>
   <si>
-    <t>Cinq Assoc. East Section 3</t>
-  </si>
-  <si>
-    <t>"Poise","Burn"</t>
-  </si>
-  <si>
-    <t>"Fixer","Cinq Association"</t>
+    <t>Kurokumo Clan Wakashu</t>
+  </si>
+  <si>
+    <t>"Syndicate","Kurokumo Clan"</t>
+  </si>
+  <si>
+    <t>LCCB Assistant Manager</t>
+  </si>
+  <si>
+    <t>"Poise","Tremor","Rupture"</t>
+  </si>
+  <si>
+    <t>"LCC","Limbus Company"</t>
   </si>
   <si>
     <t>S Corp</t>
   </si>
   <si>
-    <t>Cinq Assoc. South Section 5 Director</t>
+    <t>Liu Assoc. South Section 4</t>
+  </si>
+  <si>
+    <t>Lobotomy E.G.O::Faint Aroma &amp; Solitude</t>
+  </si>
+  <si>
+    <t>"Tremor","Sinking"</t>
   </si>
   <si>
     <t>Seven Association</t>
   </si>
   <si>
-    <t>Heishou Pack - Wei Branch</t>
-  </si>
-  <si>
-    <t>"Rupture","Sinking"</t>
-  </si>
-  <si>
-    <t>"Heishou Pack","H Corp","Heishou Pack - Wei Branch"</t>
+    <t>Lobotomy E.G.O:: Red Eyes &amp; Penitence</t>
+  </si>
+  <si>
+    <t>N Corp. E.G.O::Contempt, Awe</t>
   </si>
   <si>
     <t>Shi Association</t>
   </si>
   <si>
-    <t>Lobotomy E.G.O::In the Name of Love and Hate</t>
-  </si>
-  <si>
-    <t>"Rupture","Sinking","Charge"</t>
-  </si>
-  <si>
-    <t>Lobotomy E.G.O::Lantern</t>
+    <t>R.B. Chef De Cuisine</t>
+  </si>
+  <si>
+    <t>"The Backstreets","Syndicate","R.B"</t>
   </si>
   <si>
     <t>T Corp</t>
   </si>
   <si>
-    <t>'E.G.O Gear","Lobotomy Corp. Headquarters"</t>
+    <t>Blade Lineage Mentor</t>
   </si>
   <si>
     <t>The House of Spiders</t>
   </si>
   <si>
-    <t>N Corp. Mittelhammer</t>
+    <t>Cinq Assoc. West Section 3</t>
+  </si>
+  <si>
+    <t>"Poise","Rupture"</t>
   </si>
   <si>
     <t>The Index</t>
   </si>
   <si>
-    <t>"Bleed","Tremor"</t>
-  </si>
-  <si>
-    <t>Shi Assoc. South Section 5 Director</t>
+    <t>Dead Rabbits Boss</t>
+  </si>
+  <si>
+    <t>"Syndicate","The Dead Rabbits"</t>
+  </si>
+  <si>
+    <t>Dieci Assoc. South Section 4 Director</t>
   </si>
   <si>
     <t>The Middle</t>
   </si>
   <si>
-    <t>T Corp. Class 3 Collection Staff</t>
-  </si>
-  <si>
-    <t>"T Corp."</t>
-  </si>
-  <si>
-    <t>The Index Proxy - Effloresced E.G.O::Procuration</t>
+    <t>Liu Assoc. South Section 6</t>
   </si>
   <si>
     <t>The Pequod</t>
   </si>
   <si>
-    <t>The Manager of La Manchaland</t>
-  </si>
-  <si>
-    <t>"Second Kindred","Bloodfiend","La Manchaland"</t>
+    <t>Lobotomy E.G.O:: Hornet [Alteration]</t>
+  </si>
+  <si>
+    <t>"Burn","Bleed"</t>
   </si>
   <si>
     <t>The Pinky</t>
   </si>
   <si>
-    <t>The Middle Little Sister</t>
+    <t>N Corp. Groβhammer</t>
+  </si>
+  <si>
+    <t>"'Bleed"</t>
+  </si>
+  <si>
+    <t>R Corp. 4th Pack Rhino</t>
   </si>
   <si>
     <t>The Ring</t>
   </si>
   <si>
-    <t>"The Fingers","The Middle"</t>
+    <t>"R Corp."</t>
+  </si>
+  <si>
+    <t>Rosespanner Workshop Fixer</t>
   </si>
   <si>
     <t>The Thumb</t>
   </si>
   <si>
-    <t>"Rupture","Charge"</t>
+    <t>"Tremor","Charge"</t>
+  </si>
+  <si>
+    <t>"Fixer","Rosespanner Workshop"</t>
+  </si>
+  <si>
+    <t>The Middle Little Brother</t>
   </si>
   <si>
     <t>Tingtang Gang</t>
   </si>
   <si>
-    <t>"Tiansha Star","LCB","Limbus Company","The Pinky"</t>
-  </si>
-  <si>
-    <t>The Blade of the House of Spiders</t>
-  </si>
-  <si>
-    <t>"Poise","Bleed","Burn"</t>
-  </si>
-  <si>
-    <t>"The Fingers","The House of Spiders","The Pinky","Tiansha Star"</t>
-  </si>
-  <si>
-    <t>District 20 Yurodivy</t>
-  </si>
-  <si>
-    <t>"Syndicate","Yurodiviye"</t>
+    <t>The Prince of La Manchaland</t>
+  </si>
+  <si>
+    <t>"Bleed","Rupture"</t>
+  </si>
+  <si>
+    <t>"Third Kindred","Bloodfiend","La Manchaland"</t>
   </si>
   <si>
     <t>Twinhook Pirates</t>
   </si>
   <si>
-    <t>Drifting Blade of Hongyuan</t>
-  </si>
-  <si>
-    <t>"H Corp."</t>
+    <t>The Ring Fauvist Student</t>
+  </si>
+  <si>
+    <t>"Bleed","Sinking"</t>
+  </si>
+  <si>
+    <t>"The Fingers","School of Fauvism","The Ring"</t>
   </si>
   <si>
     <t>TLA</t>
   </si>
   <si>
-    <t>Edgar Family Chief Butler</t>
+    <t>The Thumb East Capo IIII</t>
+  </si>
+  <si>
+    <t>"Capo IIII","The Fingers","The Thumb"</t>
   </si>
   <si>
     <t>W Corp</t>
   </si>
   <si>
-    <t>"Fixer","Edgar Family"</t>
-  </si>
-  <si>
     <t>Wuthering Heights</t>
   </si>
   <si>
-    <t>Heishou Pack - Mao Branch</t>
-  </si>
-  <si>
-    <t>"Heishou Pack","H Corp","Heishou Pack - Mao Branch"</t>
-  </si>
-  <si>
     <t>Zwei Association</t>
   </si>
   <si>
-    <t>Kurokumo Clan Wakashu</t>
-  </si>
-  <si>
-    <t>"Syndicate","Kurokumo Clan"</t>
-  </si>
-  <si>
-    <t>LCCB Assistant Manager</t>
-  </si>
-  <si>
-    <t>"Poise","Tremor","Rupture"</t>
-  </si>
-  <si>
-    <t>"LCC","Limbus Company"</t>
-  </si>
-  <si>
-    <t>Liu Assoc. South Section 4</t>
-  </si>
-  <si>
-    <t>Lobotomy E.G.O::Faint Aroma &amp; Solitude</t>
-  </si>
-  <si>
-    <t>"Tremor","Sinking"</t>
-  </si>
-  <si>
-    <t>Lobotomy E.G.O:: Red Eyes &amp; Penitence</t>
-  </si>
-  <si>
-    <t>N Corp. E.G.O::Contempt, Awe</t>
-  </si>
-  <si>
-    <t>R.B. Chef De Cuisine</t>
-  </si>
-  <si>
-    <t>"The Backstreets","Syndicate","R.B"</t>
-  </si>
-  <si>
-    <t>Blade Lineage Mentor</t>
-  </si>
-  <si>
-    <t>Cinq Assoc. West Section 3</t>
-  </si>
-  <si>
-    <t>"Poise","Rupture"</t>
-  </si>
-  <si>
-    <t>Dead Rabbits Boss</t>
-  </si>
-  <si>
-    <t>"Syndicate","The Dead Rabbits"</t>
-  </si>
-  <si>
-    <t>Dieci Assoc. South Section 4 Director</t>
-  </si>
-  <si>
-    <t>Liu Assoc. South Section 6</t>
-  </si>
-  <si>
-    <t>Lobotomy E.G.O:: Hornet [Alteration]</t>
-  </si>
-  <si>
-    <t>"Burn","Bleed"</t>
-  </si>
-  <si>
-    <t>N Corp. Groβhammer</t>
-  </si>
-  <si>
-    <t>"'Bleed"</t>
-  </si>
-  <si>
-    <t>R Corp. 4th Pack Rhino</t>
-  </si>
-  <si>
-    <t>"R Corp."</t>
-  </si>
-  <si>
-    <t>Rosespanner Workshop Fixer</t>
-  </si>
-  <si>
-    <t>"Tremor","Charge"</t>
-  </si>
-  <si>
-    <t>"Fixer","Rosespanner Workshop"</t>
-  </si>
-  <si>
-    <t>The Middle Little Brother</t>
-  </si>
-  <si>
-    <t>The Prince of La Manchaland</t>
-  </si>
-  <si>
-    <t>"Bleed","Rupture"</t>
-  </si>
-  <si>
-    <t>"Third Kindred","Bloodfiend","La Manchaland"</t>
-  </si>
-  <si>
-    <t>The Ring Fauvist Student</t>
-  </si>
-  <si>
-    <t>"Bleed","Sinking"</t>
-  </si>
-  <si>
-    <t>"The Fingers","School of Fauvism","The Ring"</t>
-  </si>
-  <si>
-    <t>The Thumb East Capo IIII</t>
-  </si>
-  <si>
-    <t>"Capo IIII","The Fingers","The Thumb"</t>
-  </si>
-  <si>
     <t>Fanghunt Office Fixer</t>
   </si>
   <si>
@@ -722,6 +722,12 @@
     <t>Liu Assoc. South Section 5</t>
   </si>
   <si>
+    <t>R Corp. 4th Pack Reindeer</t>
+  </si>
+  <si>
+    <t>"Sinking","Charge"</t>
+  </si>
+  <si>
     <t>S Corp. Ch'unokkun</t>
   </si>
   <si>
@@ -845,12 +851,6 @@
     <t>Molar Boatworks Fixer</t>
   </si>
   <si>
-    <t>R Corp. 4th Pack Reindeer</t>
-  </si>
-  <si>
-    <t>"Sinking","Charge"</t>
-  </si>
-  <si>
     <t>The House of Spiders: The Middle Apprentice</t>
   </si>
   <si>
@@ -906,6 +906,132 @@
   </si>
   <si>
     <t>Zwei Assoc. South Section 5</t>
+  </si>
+  <si>
+    <t>Cinq Assoc. South Section 4 Director</t>
+  </si>
+  <si>
+    <t>Heishou Pack - You Branch</t>
+  </si>
+  <si>
+    <t>"Heishou Pack","H Corp.","Heishou Pack - You Branch"</t>
+  </si>
+  <si>
+    <t>Lobotomy E.G.O::Red Sheet</t>
+  </si>
+  <si>
+    <t>Los Mariachis Jefe</t>
+  </si>
+  <si>
+    <t>"The Backstreets","Syndicate","Los Mariachis"</t>
+  </si>
+  <si>
+    <t>The House of Spiders: The Pinky Apprentice</t>
+  </si>
+  <si>
+    <t>"The House of Spiders","The Pinky"</t>
+  </si>
+  <si>
+    <t>The One Who Shall Grip</t>
+  </si>
+  <si>
+    <t>The Thumb East Soldato II</t>
+  </si>
+  <si>
+    <t>"Soldato II","The Fingers","The Thumb"</t>
+  </si>
+  <si>
+    <t>Zwei Assoc. South Section 6</t>
+  </si>
+  <si>
+    <t>Cinq Assoc. South Section 4</t>
+  </si>
+  <si>
+    <t>G Corp. Head Manager</t>
+  </si>
+  <si>
+    <t>"G Corp."</t>
+  </si>
+  <si>
+    <t>"Heishou Pack","H Corp.","Heishou Pack - Mao Branch"</t>
+  </si>
+  <si>
+    <t>LCA Udjat Outis</t>
+  </si>
+  <si>
+    <t>"LCA","Limbus Company"</t>
+  </si>
+  <si>
+    <t>Lobotomy E.G.O::Magic Bullet</t>
+  </si>
+  <si>
+    <t>Seven Assoc. South Section 6 Director</t>
+  </si>
+  <si>
+    <t>T Corp. Class 3 VDCU Staff</t>
+  </si>
+  <si>
+    <t>The Barber of La Manchaland</t>
+  </si>
+  <si>
+    <t>The House of Spiders: The Middle Nursefather</t>
+  </si>
+  <si>
+    <t>"The Fingers","The Middle","The House of Spiders"</t>
+  </si>
+  <si>
+    <t>W Corp. L3 Cleanup Captain</t>
+  </si>
+  <si>
+    <t>Wuthering Heights Chief Butler</t>
+  </si>
+  <si>
+    <t>Dawn Office Rep</t>
+  </si>
+  <si>
+    <t>Edgar Family Heir</t>
+  </si>
+  <si>
+    <t>"Edgar Family"</t>
+  </si>
+  <si>
+    <t>Firefist Office Survivor</t>
+  </si>
+  <si>
+    <t>"Fixer"</t>
+  </si>
+  <si>
+    <t>G Corp. Manager Corporal</t>
+  </si>
+  <si>
+    <t>LCE E.G.O::AEDD</t>
+  </si>
+  <si>
+    <t>Lobotomy E.G.O::Lamp</t>
+  </si>
+  <si>
+    <t>"Burn","Sinking"</t>
+  </si>
+  <si>
+    <t>Night Awls Capitano</t>
+  </si>
+  <si>
+    <t>"Syndicate","Night Awls"</t>
+  </si>
+  <si>
+    <t>R.B. Sous-chef</t>
+  </si>
+  <si>
+    <t>"Rupture","Tremor","Charge"</t>
+  </si>
+  <si>
+    <t>The Priest of La Manchaland</t>
+  </si>
+  <si>
+    <t>Twinhook Pirates First Mate</t>
+  </si>
+  <si>
+    <t>"Syndicate","Twinhook Pirates"</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1300,7 @@
     <col customWidth="1" min="2" max="2" width="38.75"/>
     <col customWidth="1" min="3" max="3" width="6.38"/>
     <col customWidth="1" min="4" max="4" width="6.63"/>
-    <col customWidth="1" min="5" max="5" width="21.0"/>
+    <col customWidth="1" min="5" max="5" width="22.63"/>
     <col customWidth="1" min="6" max="6" width="48.63"/>
     <col customWidth="1" min="7" max="7" width="7.63"/>
     <col customWidth="1" min="8" max="8" width="8.5"/>
@@ -1185,28 +1311,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
@@ -1214,7 +1340,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
@@ -1223,10 +1349,10 @@
         <v>8.0</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="G2" s="1">
         <v>1.0</v>
@@ -1243,19 +1369,19 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="D3" s="1">
-        <v>60.0</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="G3" s="1">
         <v>1.0</v>
@@ -1272,19 +1398,22 @@
         <v>1.0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>35</v>
+      <c r="G4" s="1">
+        <v>4.0</v>
       </c>
       <c r="H4" s="1">
         <v>4.0</v>
@@ -1298,7 +1427,7 @@
         <v>1.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1">
         <v>3.0</v>
@@ -1307,10 +1436,10 @@
         <v>55.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1">
         <v>2.0</v>
@@ -1327,19 +1456,19 @@
         <v>1.0</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C6" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="D6" s="1">
-        <v>60.0</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="G6" s="1">
         <v>6.0</v>
@@ -1356,19 +1485,19 @@
         <v>1.0</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="D7" s="1">
-        <v>60.0</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="G7" s="1">
         <v>7.0</v>
@@ -1385,7 +1514,7 @@
         <v>1.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1">
         <v>2.0</v>
@@ -1394,10 +1523,10 @@
         <v>60.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G8" s="1">
         <v>5.0</v>
@@ -1414,7 +1543,7 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C9" s="1">
         <v>3.0</v>
@@ -1423,10 +1552,13 @@
         <v>60.0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="G9" s="1">
+        <v>5.0</v>
       </c>
       <c r="H9" s="1">
         <v>2.0</v>
@@ -1440,7 +1572,7 @@
         <v>1.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1">
         <v>3.0</v>
@@ -1449,10 +1581,13 @@
         <v>60.0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4.0</v>
       </c>
       <c r="H10" s="1">
         <v>1.0</v>
@@ -1466,7 +1601,7 @@
         <v>1.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C11" s="1">
         <v>2.0</v>
@@ -1475,10 +1610,13 @@
         <v>11.0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2.0</v>
       </c>
       <c r="H11" s="1">
         <v>3.0</v>
@@ -1492,7 +1630,7 @@
         <v>1.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C12" s="1">
         <v>3.0</v>
@@ -1501,10 +1639,10 @@
         <v>55.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G12" s="1">
         <v>6.0</v>
@@ -1521,7 +1659,7 @@
         <v>1.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C13" s="1">
         <v>2.0</v>
@@ -1530,10 +1668,13 @@
         <v>33.0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1.0</v>
       </c>
       <c r="H13" s="1">
         <v>4.0</v>
@@ -1547,7 +1688,7 @@
         <v>1.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C14" s="1">
         <v>3.0</v>
@@ -1556,10 +1697,10 @@
         <v>60.0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G14" s="1">
         <v>7.0</v>
@@ -1576,7 +1717,7 @@
         <v>1.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C15" s="1">
         <v>2.0</v>
@@ -1585,10 +1726,10 @@
         <v>60.0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G15" s="1">
         <v>5.0</v>
@@ -1605,7 +1746,7 @@
         <v>1.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C16" s="1">
         <v>3.0</v>
@@ -1614,10 +1755,13 @@
         <v>60.0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3.0</v>
       </c>
       <c r="H16" s="1">
         <v>2.0</v>
@@ -1631,7 +1775,7 @@
         <v>1.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C17" s="1">
         <v>3.0</v>
@@ -1640,10 +1784,13 @@
         <v>55.0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2.0</v>
       </c>
       <c r="H17" s="1">
         <v>2.0</v>
@@ -1657,7 +1804,7 @@
         <v>2.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="1">
         <v>1.0</v>
@@ -1666,7 +1813,7 @@
         <v>17.0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" s="1">
         <v>1.0</v>
@@ -1683,7 +1830,7 @@
         <v>2.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" s="1">
         <v>3.0</v>
@@ -1692,10 +1839,13 @@
         <v>60.0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="G19" s="1">
+        <v>3.0</v>
       </c>
       <c r="H19" s="1">
         <v>3.0</v>
@@ -1709,7 +1859,7 @@
         <v>2.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C20" s="1">
         <v>3.0</v>
@@ -1718,10 +1868,10 @@
         <v>60.0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G20" s="1">
         <v>7.0</v>
@@ -1738,7 +1888,7 @@
         <v>2.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C21" s="1">
         <v>3.0</v>
@@ -1747,10 +1897,10 @@
         <v>60.0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G21" s="1">
         <v>6.0</v>
@@ -1767,7 +1917,7 @@
         <v>2.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C22" s="1">
         <v>3.0</v>
@@ -1776,10 +1926,10 @@
         <v>60.0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G22" s="1">
         <v>5.0</v>
@@ -1796,7 +1946,7 @@
         <v>2.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C23" s="1">
         <v>2.0</v>
@@ -1805,10 +1955,10 @@
         <v>1.0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G23" s="1">
         <v>1.0</v>
@@ -1825,7 +1975,7 @@
         <v>2.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C24" s="1">
         <v>3.0</v>
@@ -1834,10 +1984,13 @@
         <v>60.0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2.0</v>
       </c>
       <c r="H24" s="1">
         <v>2.0</v>
@@ -1851,7 +2004,7 @@
         <v>2.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C25" s="1">
         <v>3.0</v>
@@ -1860,10 +2013,13 @@
         <v>60.0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
+      </c>
+      <c r="G25" s="1">
+        <v>4.0</v>
       </c>
       <c r="H25" s="1">
         <v>2.0</v>
@@ -1877,7 +2033,7 @@
         <v>2.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C26" s="1">
         <v>3.0</v>
@@ -1886,10 +2042,13 @@
         <v>1.0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1.0</v>
       </c>
       <c r="H26" s="1">
         <v>3.0</v>
@@ -1903,7 +2062,7 @@
         <v>2.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C27" s="1">
         <v>3.0</v>
@@ -1912,10 +2071,13 @@
         <v>60.0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
+      </c>
+      <c r="G27" s="1">
+        <v>6.0</v>
       </c>
       <c r="H27" s="1">
         <v>2.0</v>
@@ -1929,7 +2091,7 @@
         <v>2.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C28" s="1">
         <v>3.0</v>
@@ -1938,10 +2100,10 @@
         <v>60.0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="G28" s="1">
         <v>7.0</v>
@@ -1958,7 +2120,7 @@
         <v>2.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C29" s="1">
         <v>3.0</v>
@@ -1967,10 +2129,10 @@
         <v>60.0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G29" s="1">
         <v>7.0</v>
@@ -1987,7 +2149,7 @@
         <v>2.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C30" s="1">
         <v>3.0</v>
@@ -1996,10 +2158,10 @@
         <v>8.0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="G30" s="1">
         <v>1.0</v>
@@ -2016,7 +2178,7 @@
         <v>2.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C31" s="1">
         <v>2.0</v>
@@ -2025,10 +2187,13 @@
         <v>1.0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
+      </c>
+      <c r="G31" s="1">
+        <v>1.0</v>
       </c>
       <c r="H31" s="1">
         <v>4.0</v>
@@ -2042,7 +2207,7 @@
         <v>2.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C32" s="1">
         <v>2.0</v>
@@ -2051,10 +2216,10 @@
         <v>60.0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="G32" s="1">
         <v>4.0</v>
@@ -2071,7 +2236,7 @@
         <v>2.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C33" s="1">
         <v>2.0</v>
@@ -2080,7 +2245,10 @@
         <v>1.0</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>126</v>
+        <v>113</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2.0</v>
       </c>
       <c r="H33" s="1">
         <v>4.0</v>
@@ -2094,7 +2262,7 @@
         <v>3.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C34" s="1">
         <v>1.0</v>
@@ -2103,10 +2271,10 @@
         <v>6.0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G34" s="1">
         <v>1.0</v>
@@ -2123,19 +2291,22 @@
         <v>3.0</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D35" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D35" s="1">
-        <v>60.0</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>32</v>
+      <c r="G35" s="1">
+        <v>3.0</v>
       </c>
       <c r="H35" s="1">
         <v>3.0</v>
@@ -2149,7 +2320,7 @@
         <v>3.0</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C36" s="1">
         <v>3.0</v>
@@ -2158,10 +2329,13 @@
         <v>55.0</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>131</v>
+        <v>118</v>
+      </c>
+      <c r="G36" s="1">
+        <v>5.0</v>
       </c>
       <c r="H36" s="1">
         <v>3.0</v>
@@ -2175,7 +2349,7 @@
         <v>3.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C37" s="1">
         <v>3.0</v>
@@ -2184,7 +2358,10 @@
         <v>1.0</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>131</v>
+        <v>118</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2.0</v>
       </c>
       <c r="H37" s="1">
         <v>3.0</v>
@@ -2198,7 +2375,7 @@
         <v>3.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C38" s="1">
         <v>3.0</v>
@@ -2207,10 +2384,10 @@
         <v>60.0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G38" s="1">
         <v>6.0</v>
@@ -2227,7 +2404,7 @@
         <v>3.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C39" s="1">
         <v>3.0</v>
@@ -2236,10 +2413,13 @@
         <v>60.0</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="G39" s="1">
+        <v>6.0</v>
       </c>
       <c r="H39" s="1">
         <v>1.0</v>
@@ -2253,7 +2433,7 @@
         <v>3.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C40" s="1">
         <v>2.0</v>
@@ -2262,10 +2442,13 @@
         <v>8.0</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2.0</v>
       </c>
       <c r="H40" s="1">
         <v>3.0</v>
@@ -2279,7 +2462,7 @@
         <v>3.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C41" s="1">
         <v>2.0</v>
@@ -2288,10 +2471,13 @@
         <v>60.0</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1.0</v>
       </c>
       <c r="H41" s="1">
         <v>5.0</v>
@@ -2305,7 +2491,7 @@
         <v>3.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C42" s="1">
         <v>2.0</v>
@@ -2314,10 +2500,13 @@
         <v>1.0</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1.0</v>
       </c>
       <c r="H42" s="1">
         <v>4.0</v>
@@ -2331,7 +2520,7 @@
         <v>3.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C43" s="1">
         <v>3.0</v>
@@ -2340,10 +2529,13 @@
         <v>60.0</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>151</v>
+        <v>136</v>
+      </c>
+      <c r="G43" s="1">
+        <v>4.0</v>
       </c>
       <c r="H43" s="1">
         <v>2.0</v>
@@ -2357,7 +2549,7 @@
         <v>3.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C44" s="1">
         <v>3.0</v>
@@ -2366,10 +2558,10 @@
         <v>60.0</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G44" s="1">
         <v>7.0</v>
@@ -2386,7 +2578,7 @@
         <v>3.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C45" s="1">
         <v>3.0</v>
@@ -2395,10 +2587,10 @@
         <v>60.0</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="G45" s="1">
         <v>5.0</v>
@@ -2415,7 +2607,7 @@
         <v>3.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="C46" s="1">
         <v>3.0</v>
@@ -2424,10 +2616,13 @@
         <v>60.0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
+      </c>
+      <c r="G46" s="1">
+        <v>3.0</v>
       </c>
       <c r="H46" s="1">
         <v>2.0</v>
@@ -2441,7 +2636,7 @@
         <v>3.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C47" s="1">
         <v>3.0</v>
@@ -2450,10 +2645,13 @@
         <v>1.0</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1.0</v>
       </c>
       <c r="H47" s="1">
         <v>3.0</v>
@@ -2467,7 +2665,7 @@
         <v>4.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C48" s="1">
         <v>1.0</v>
@@ -2476,10 +2674,10 @@
         <v>10.0</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="G48" s="1">
         <v>1.0</v>
@@ -2496,7 +2694,7 @@
         <v>4.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="C49" s="1">
         <v>3.0</v>
@@ -2505,10 +2703,10 @@
         <v>60.0</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="G49" s="1">
         <v>7.0</v>
@@ -2525,7 +2723,7 @@
         <v>4.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="C50" s="1">
         <v>2.0</v>
@@ -2534,10 +2732,13 @@
         <v>10.0</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>168</v>
+        <v>153</v>
+      </c>
+      <c r="G50" s="1">
+        <v>4.0</v>
       </c>
       <c r="H50" s="1">
         <v>3.0</v>
@@ -2551,7 +2752,7 @@
         <v>4.0</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="C51" s="1">
         <v>3.0</v>
@@ -2560,10 +2761,10 @@
         <v>55.0</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="G51" s="1">
         <v>6.0</v>
@@ -2580,7 +2781,7 @@
         <v>4.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="C52" s="1">
         <v>3.0</v>
@@ -2589,10 +2790,10 @@
         <v>1.0</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="G52" s="1">
         <v>4.0</v>
@@ -2609,7 +2810,7 @@
         <v>4.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="C53" s="1">
         <v>3.0</v>
@@ -2618,13 +2819,13 @@
         <v>60.0</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="G53" s="1">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="H53" s="1">
         <v>1.0</v>
@@ -2638,7 +2839,7 @@
         <v>4.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="C54" s="1">
         <v>3.0</v>
@@ -2647,10 +2848,13 @@
         <v>55.0</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>181</v>
+        <v>164</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1.0</v>
       </c>
       <c r="H54" s="1">
         <v>3.0</v>
@@ -2664,7 +2868,7 @@
         <v>4.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="C55" s="1">
         <v>2.0</v>
@@ -2673,10 +2877,13 @@
         <v>23.0</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>184</v>
+        <v>167</v>
+      </c>
+      <c r="G55" s="1">
+        <v>1.0</v>
       </c>
       <c r="H55" s="1">
         <v>4.0</v>
@@ -2690,7 +2897,7 @@
         <v>4.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="C56" s="1">
         <v>2.0</v>
@@ -2699,10 +2906,13 @@
         <v>5.0</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="G56" s="1">
+        <v>2.0</v>
       </c>
       <c r="H56" s="1">
         <v>5.0</v>
@@ -2716,7 +2926,7 @@
         <v>4.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="C57" s="1">
         <v>3.0</v>
@@ -2725,10 +2935,13 @@
         <v>60.0</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="G57" s="1">
+        <v>7.0</v>
       </c>
       <c r="H57" s="1">
         <v>1.0</v>
@@ -2742,7 +2955,7 @@
         <v>4.0</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="C58" s="1">
         <v>3.0</v>
@@ -2751,10 +2964,13 @@
         <v>60.0</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="G58" s="1">
+        <v>4.0</v>
       </c>
       <c r="H58" s="1">
         <v>2.0</v>
@@ -2768,7 +2984,7 @@
         <v>4.0</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C59" s="1">
         <v>3.0</v>
@@ -2777,10 +2993,13 @@
         <v>60.0</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
+      </c>
+      <c r="G59" s="1">
+        <v>6.0</v>
       </c>
       <c r="H59" s="1">
         <v>2.0</v>
@@ -2794,7 +3013,7 @@
         <v>4.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C60" s="1">
         <v>3.0</v>
@@ -2803,10 +3022,10 @@
         <v>1.0</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="G60" s="1">
         <v>1.0</v>
@@ -2823,7 +3042,7 @@
         <v>4.0</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C61" s="1">
         <v>2.0</v>
@@ -2832,10 +3051,13 @@
         <v>13.0</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
+      </c>
+      <c r="G61" s="1">
+        <v>1.0</v>
       </c>
       <c r="H61" s="1">
         <v>4.0</v>
@@ -2849,7 +3071,7 @@
         <v>4.0</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C62" s="1">
         <v>3.0</v>
@@ -2858,10 +3080,13 @@
         <v>60.0</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
+      </c>
+      <c r="G62" s="1">
+        <v>2.0</v>
       </c>
       <c r="H62" s="1">
         <v>3.0</v>
@@ -2875,7 +3100,7 @@
         <v>5.0</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C63" s="1">
         <v>1.0</v>
@@ -2884,10 +3109,10 @@
         <v>4.0</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G63" s="1">
         <v>1.0</v>
@@ -2904,7 +3129,7 @@
         <v>5.0</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C64" s="1">
         <v>3.0</v>
@@ -2913,10 +3138,13 @@
         <v>60.0</v>
       </c>
       <c r="E64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>32</v>
+      <c r="G64" s="1">
+        <v>3.0</v>
       </c>
       <c r="H64" s="1">
         <v>1.0</v>
@@ -2930,7 +3158,7 @@
         <v>5.0</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="C65" s="1">
         <v>3.0</v>
@@ -2939,10 +3167,10 @@
         <v>60.0</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="G65" s="1">
         <v>5.0</v>
@@ -2959,7 +3187,7 @@
         <v>5.0</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C66" s="1">
         <v>2.0</v>
@@ -2968,10 +3196,10 @@
         <v>4.0</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="G66" s="1">
         <v>4.0</v>
@@ -2988,7 +3216,7 @@
         <v>5.0</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C67" s="1">
         <v>3.0</v>
@@ -2997,10 +3225,13 @@
         <v>60.0</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="G67" s="1">
+        <v>4.0</v>
       </c>
       <c r="H67" s="1">
         <v>3.0</v>
@@ -3014,7 +3245,7 @@
         <v>5.0</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C68" s="1">
         <v>2.0</v>
@@ -3023,10 +3254,13 @@
         <v>1.0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1.0</v>
       </c>
       <c r="H68" s="1">
         <v>4.0</v>
@@ -3040,7 +3274,7 @@
         <v>5.0</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C69" s="1">
         <v>3.0</v>
@@ -3049,10 +3283,13 @@
         <v>60.0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="G69" s="1">
+        <v>7.0</v>
       </c>
       <c r="H69" s="1">
         <v>0.0</v>
@@ -3066,7 +3303,7 @@
         <v>5.0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C70" s="1">
         <v>3.0</v>
@@ -3075,10 +3312,10 @@
         <v>1.0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="G70" s="1">
         <v>1.0</v>
@@ -3095,7 +3332,7 @@
         <v>5.0</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C71" s="1">
         <v>3.0</v>
@@ -3104,10 +3341,13 @@
         <v>1.0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>204</v>
+        <v>197</v>
+      </c>
+      <c r="G71" s="1">
+        <v>2.0</v>
       </c>
       <c r="H71" s="1">
         <v>3.0</v>
@@ -3121,7 +3361,7 @@
         <v>5.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C72" s="1">
         <v>2.0</v>
@@ -3130,10 +3370,13 @@
         <v>1.0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
+      </c>
+      <c r="G72" s="1">
+        <v>2.0</v>
       </c>
       <c r="H72" s="1">
         <v>4.0</v>
@@ -3147,7 +3390,7 @@
         <v>5.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C73" s="1">
         <v>2.0</v>
@@ -3156,10 +3399,13 @@
         <v>60.0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
+      </c>
+      <c r="G73" s="1">
+        <v>3.0</v>
       </c>
       <c r="H73" s="1">
         <v>3.0</v>
@@ -3173,7 +3419,7 @@
         <v>5.0</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C74" s="1">
         <v>3.0</v>
@@ -3182,10 +3428,10 @@
         <v>60.0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G74" s="1">
         <v>6.0</v>
@@ -3202,7 +3448,7 @@
         <v>5.0</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C75" s="1">
         <v>3.0</v>
@@ -3211,10 +3457,10 @@
         <v>60.0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G75" s="1">
         <v>7.0</v>
@@ -3231,7 +3477,7 @@
         <v>5.0</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C76" s="1">
         <v>3.0</v>
@@ -3240,10 +3486,10 @@
         <v>60.0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G76" s="1">
         <v>5.0</v>
@@ -3260,7 +3506,7 @@
         <v>5.0</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C77" s="1">
         <v>3.0</v>
@@ -3269,10 +3515,13 @@
         <v>60.0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
+      </c>
+      <c r="G77" s="1">
+        <v>1.0</v>
       </c>
       <c r="H77" s="1">
         <v>5.0</v>
@@ -3286,7 +3535,7 @@
         <v>6.0</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C78" s="1">
         <v>1.0</v>
@@ -3295,10 +3544,10 @@
         <v>55.0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G78" s="1">
         <v>1.0</v>
@@ -3315,7 +3564,7 @@
         <v>6.0</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="C79" s="1">
         <v>3.0</v>
@@ -3324,16 +3573,19 @@
         <v>55.0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="G79" s="1">
         <v>7.0</v>
       </c>
       <c r="H79" s="1">
         <v>2.0</v>
+      </c>
+      <c r="I79" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="80">
@@ -3341,7 +3593,7 @@
         <v>6.0</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C80" s="1">
         <v>3.0</v>
@@ -3350,13 +3602,19 @@
         <v>55.0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="G80" s="1">
+        <v>4.0</v>
       </c>
       <c r="H80" s="1">
         <v>3.0</v>
+      </c>
+      <c r="I80" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="81">
@@ -3364,7 +3622,7 @@
         <v>6.0</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="C81" s="1">
         <v>3.0</v>
@@ -3373,13 +3631,19 @@
         <v>60.0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>168</v>
+        <v>153</v>
+      </c>
+      <c r="G81" s="1">
+        <v>4.0</v>
       </c>
       <c r="H81" s="1">
         <v>2.0</v>
+      </c>
+      <c r="I81" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="82">
@@ -3396,7 +3660,7 @@
         <v>6.0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>218</v>
@@ -3406,6 +3670,9 @@
       </c>
       <c r="H82" s="1">
         <v>3.0</v>
+      </c>
+      <c r="I82" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="83">
@@ -3422,7 +3689,7 @@
         <v>60.0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>220</v>
@@ -3431,6 +3698,9 @@
         <v>5.0</v>
       </c>
       <c r="H83" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I83" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -3448,13 +3718,19 @@
         <v>6.0</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>222</v>
       </c>
+      <c r="G84" s="1">
+        <v>2.0</v>
+      </c>
       <c r="H84" s="1">
         <v>3.0</v>
+      </c>
+      <c r="I84" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="85">
@@ -3471,7 +3747,7 @@
         <v>1.0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>224</v>
@@ -3481,6 +3757,9 @@
       </c>
       <c r="H85" s="1">
         <v>2.0</v>
+      </c>
+      <c r="I85" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="86">
@@ -3488,7 +3767,7 @@
         <v>6.0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="C86" s="1">
         <v>2.0</v>
@@ -3497,16 +3776,19 @@
         <v>5.0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="G86" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H86" s="1">
         <v>4.0</v>
+      </c>
+      <c r="I86" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="87">
@@ -3523,16 +3805,19 @@
         <v>4.0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G87" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H87" s="1">
         <v>4.0</v>
+      </c>
+      <c r="I87" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="88">
@@ -3549,16 +3834,19 @@
         <v>60.0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>62</v>
+        <v>227</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="G88" s="1">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="H88" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
+      </c>
+      <c r="I88" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="89">
@@ -3575,16 +3863,19 @@
         <v>60.0</v>
       </c>
       <c r="E89" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="G89" s="1">
         <v>7.0</v>
       </c>
       <c r="H89" s="1">
-        <v>0.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="I89" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="90">
@@ -3601,16 +3892,19 @@
         <v>60.0</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>95</v>
+        <v>231</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>231</v>
+        <v>101</v>
       </c>
       <c r="G90" s="1">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H90" s="1">
         <v>0.0</v>
+      </c>
+      <c r="I90" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="91">
@@ -3624,19 +3918,22 @@
         <v>3.0</v>
       </c>
       <c r="D91" s="1">
-        <v>8.0</v>
+        <v>60.0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>233</v>
       </c>
       <c r="G91" s="1">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H91" s="1">
-        <v>3.0</v>
+        <v>0.0</v>
+      </c>
+      <c r="I91" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="92">
@@ -3644,48 +3941,57 @@
         <v>6.0</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>119</v>
+        <v>234</v>
       </c>
       <c r="C92" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D92" s="1">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>80</v>
+        <v>235</v>
+      </c>
+      <c r="G92" s="1">
+        <v>1.0</v>
       </c>
       <c r="H92" s="1">
-        <v>4.0</v>
+        <v>3.0</v>
+      </c>
+      <c r="I92" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="C93" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D93" s="1">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="G93" s="1">
         <v>1.0</v>
       </c>
       <c r="H93" s="1">
-        <v>5.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="I93" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="94">
@@ -3693,25 +3999,28 @@
         <v>7.0</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>234</v>
+        <v>24</v>
       </c>
       <c r="C94" s="1">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="D94" s="1">
-        <v>60.0</v>
+        <v>18.0</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>220</v>
+        <v>27</v>
       </c>
       <c r="G94" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H94" s="1">
         <v>5.0</v>
       </c>
-      <c r="H94" s="1">
-        <v>0.0</v>
+      <c r="I94" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="95">
@@ -3719,7 +4028,7 @@
         <v>7.0</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C95" s="1">
         <v>3.0</v>
@@ -3728,16 +4037,19 @@
         <v>60.0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>236</v>
+        <v>29</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="G95" s="1">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="H95" s="1">
-        <v>2.0</v>
+        <v>0.0</v>
+      </c>
+      <c r="I95" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="96">
@@ -3745,7 +4057,7 @@
         <v>7.0</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>180</v>
+        <v>237</v>
       </c>
       <c r="C96" s="1">
         <v>3.0</v>
@@ -3754,16 +4066,19 @@
         <v>60.0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>76</v>
+        <v>238</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>181</v>
+        <v>239</v>
       </c>
       <c r="G96" s="1">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H96" s="1">
         <v>2.0</v>
+      </c>
+      <c r="I96" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="97">
@@ -3771,25 +4086,28 @@
         <v>7.0</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>238</v>
+        <v>163</v>
       </c>
       <c r="C97" s="1">
         <v>3.0</v>
       </c>
       <c r="D97" s="1">
-        <v>55.0</v>
+        <v>60.0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>239</v>
+        <v>164</v>
       </c>
       <c r="G97" s="1">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H97" s="1">
-        <v>5.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="I97" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="98">
@@ -3800,22 +4118,25 @@
         <v>240</v>
       </c>
       <c r="C98" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D98" s="1">
-        <v>10.0</v>
+        <v>55.0</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>102</v>
+        <v>241</v>
       </c>
       <c r="G98" s="1">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H98" s="1">
-        <v>3.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="I98" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="99">
@@ -3823,25 +4144,28 @@
         <v>7.0</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C99" s="1">
         <v>2.0</v>
       </c>
       <c r="D99" s="1">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="G99" s="1">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H99" s="1">
-        <v>4.0</v>
+        <v>3.0</v>
+      </c>
+      <c r="I99" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="100">
@@ -3849,22 +4173,28 @@
         <v>7.0</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C100" s="1">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D100" s="1">
         <v>1.0</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>243</v>
+        <v>72</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>204</v>
+        <v>107</v>
+      </c>
+      <c r="G100" s="1">
+        <v>1.0</v>
       </c>
       <c r="H100" s="1">
-        <v>3.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="I100" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="101">
@@ -3872,22 +4202,28 @@
         <v>7.0</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>104</v>
+        <v>244</v>
       </c>
       <c r="C101" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D101" s="1">
-        <v>55.0</v>
+        <v>1.0</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>48</v>
+        <v>245</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>66</v>
+        <v>197</v>
+      </c>
+      <c r="G101" s="1">
+        <v>1.0</v>
       </c>
       <c r="H101" s="1">
         <v>3.0</v>
+      </c>
+      <c r="I101" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="102">
@@ -3895,22 +4231,28 @@
         <v>7.0</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>244</v>
+        <v>94</v>
       </c>
       <c r="C102" s="1">
         <v>2.0</v>
       </c>
       <c r="D102" s="1">
-        <v>1.0</v>
+        <v>55.0</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>107</v>
+        <v>63</v>
+      </c>
+      <c r="G102" s="1">
+        <v>2.0</v>
       </c>
       <c r="H102" s="1">
-        <v>4.0</v>
+        <v>3.0</v>
+      </c>
+      <c r="I102" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="103">
@@ -3918,24 +4260,27 @@
         <v>7.0</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C103" s="1">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D103" s="1">
-        <v>60.0</v>
+        <v>1.0</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>246</v>
+        <v>97</v>
       </c>
       <c r="G103" s="1">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H103" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I103" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -3953,16 +4298,19 @@
         <v>60.0</v>
       </c>
       <c r="E104" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="G104" s="1">
         <v>7.0</v>
       </c>
       <c r="H104" s="1">
-        <v>0.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="I104" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="105">
@@ -3979,16 +4327,19 @@
         <v>60.0</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>62</v>
+        <v>250</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>250</v>
+        <v>142</v>
       </c>
       <c r="G105" s="1">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="H105" s="1">
-        <v>2.0</v>
+        <v>0.0</v>
+      </c>
+      <c r="I105" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="106">
@@ -4005,16 +4356,19 @@
         <v>60.0</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="G106" s="1">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="H106" s="1">
         <v>2.0</v>
+      </c>
+      <c r="I106" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="107">
@@ -4022,7 +4376,7 @@
         <v>7.0</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C107" s="1">
         <v>3.0</v>
@@ -4031,16 +4385,19 @@
         <v>60.0</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>253</v>
+        <v>75</v>
       </c>
       <c r="G107" s="1">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H107" s="1">
         <v>2.0</v>
+      </c>
+      <c r="I107" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="108">
@@ -4057,39 +4414,48 @@
         <v>60.0</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>255</v>
       </c>
+      <c r="G108" s="1">
+        <v>4.0</v>
+      </c>
       <c r="H108" s="1">
-        <v>3.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="I108" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>25</v>
+        <v>256</v>
       </c>
       <c r="C109" s="1">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="D109" s="1">
-        <v>6.0</v>
+        <v>60.0</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>28</v>
+        <v>257</v>
       </c>
       <c r="G109" s="1">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="H109" s="1">
-        <v>5.0</v>
+        <v>3.0</v>
+      </c>
+      <c r="I109" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="110">
@@ -4097,25 +4463,28 @@
         <v>8.0</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>256</v>
+        <v>24</v>
       </c>
       <c r="C110" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D110" s="1">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
       <c r="E110" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F110" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="G110" s="1">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H110" s="1">
-        <v>4.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="I110" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="111">
@@ -4123,25 +4492,28 @@
         <v>8.0</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C111" s="1">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D111" s="1">
-        <v>60.0</v>
+        <v>20.0</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>258</v>
+        <v>159</v>
       </c>
       <c r="G111" s="1">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="H111" s="1">
-        <v>2.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="I111" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="112">
@@ -4158,13 +4530,19 @@
         <v>60.0</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>260</v>
       </c>
+      <c r="G112" s="1">
+        <v>6.0</v>
+      </c>
       <c r="H112" s="1">
-        <v>0.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="I112" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="113">
@@ -4181,16 +4559,19 @@
         <v>60.0</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>181</v>
+        <v>262</v>
       </c>
       <c r="G113" s="1">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H113" s="1">
-        <v>2.0</v>
+        <v>0.0</v>
+      </c>
+      <c r="I113" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="114">
@@ -4198,25 +4579,28 @@
         <v>8.0</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>182</v>
+        <v>263</v>
       </c>
       <c r="C114" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D114" s="1">
-        <v>1.0</v>
+        <v>60.0</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>262</v>
+        <v>72</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="G114" s="1">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H114" s="1">
-        <v>4.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="I114" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="115">
@@ -4224,24 +4608,27 @@
         <v>8.0</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>263</v>
+        <v>165</v>
       </c>
       <c r="C115" s="1">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D115" s="1">
-        <v>60.0</v>
+        <v>1.0</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>62</v>
+        <v>264</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>264</v>
+        <v>167</v>
       </c>
       <c r="G115" s="1">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H115" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I115" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -4250,22 +4637,28 @@
         <v>8.0</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="C116" s="1">
         <v>3.0</v>
       </c>
       <c r="D116" s="1">
-        <v>4.0</v>
+        <v>60.0</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>52</v>
+        <v>266</v>
+      </c>
+      <c r="G116" s="1">
+        <v>7.0</v>
       </c>
       <c r="H116" s="1">
-        <v>3.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="I116" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="117">
@@ -4273,25 +4666,28 @@
         <v>8.0</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>265</v>
+        <v>169</v>
       </c>
       <c r="C117" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D117" s="1">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>262</v>
+        <v>48</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>239</v>
+        <v>49</v>
       </c>
       <c r="G117" s="1">
         <v>2.0</v>
       </c>
       <c r="H117" s="1">
-        <v>5.0</v>
+        <v>3.0</v>
+      </c>
+      <c r="I117" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="118">
@@ -4299,25 +4695,28 @@
         <v>8.0</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C118" s="1">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D118" s="1">
         <v>1.0</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>59</v>
+        <v>241</v>
       </c>
       <c r="G118" s="1">
         <v>2.0</v>
       </c>
       <c r="H118" s="1">
-        <v>3.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="I118" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="119">
@@ -4325,22 +4724,28 @@
         <v>8.0</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C119" s="1">
         <v>3.0</v>
       </c>
       <c r="D119" s="1">
-        <v>55.0</v>
+        <v>1.0</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>268</v>
+        <v>171</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>204</v>
+        <v>56</v>
+      </c>
+      <c r="G119" s="1">
+        <v>2.0</v>
       </c>
       <c r="H119" s="1">
         <v>3.0</v>
+      </c>
+      <c r="I119" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="120">
@@ -4348,22 +4753,28 @@
         <v>8.0</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="C120" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D120" s="1">
-        <v>19.0</v>
+        <v>55.0</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>30</v>
+        <v>227</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>107</v>
+        <v>197</v>
+      </c>
+      <c r="G120" s="1">
+        <v>1.0</v>
       </c>
       <c r="H120" s="1">
-        <v>4.0</v>
+        <v>3.0</v>
+      </c>
+      <c r="I120" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="121">
@@ -4371,24 +4782,27 @@
         <v>8.0</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="C121" s="1">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="D121" s="1">
-        <v>60.0</v>
+        <v>19.0</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>270</v>
+        <v>29</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>271</v>
+        <v>97</v>
       </c>
       <c r="G121" s="1">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H121" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I121" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -4397,25 +4811,28 @@
         <v>8.0</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C122" s="1">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="D122" s="1">
-        <v>55.0</v>
+        <v>60.0</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="G122" s="1">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="H122" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="I122" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="123">
@@ -4423,7 +4840,7 @@
         <v>8.0</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C123" s="1">
         <v>3.0</v>
@@ -4432,39 +4849,48 @@
         <v>55.0</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>58</v>
+        <v>273</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>126</v>
+        <v>252</v>
+      </c>
+      <c r="G123" s="1">
+        <v>3.0</v>
       </c>
       <c r="H123" s="1">
         <v>2.0</v>
+      </c>
+      <c r="I123" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>25</v>
+        <v>274</v>
       </c>
       <c r="C124" s="1">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="D124" s="1">
-        <v>8.0</v>
+        <v>55.0</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="G124" s="1">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H124" s="1">
-        <v>5.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="I124" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="125">
@@ -4472,22 +4898,28 @@
         <v>9.0</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>275</v>
+        <v>24</v>
       </c>
       <c r="C125" s="1">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="D125" s="1">
-        <v>55.0</v>
+        <v>8.0</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>276</v>
+        <v>27</v>
+      </c>
+      <c r="G125" s="1">
+        <v>1.0</v>
       </c>
       <c r="H125" s="1">
-        <v>2.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="I125" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="126">
@@ -4495,22 +4927,28 @@
         <v>9.0</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>33</v>
+        <v>275</v>
       </c>
       <c r="C126" s="1">
         <v>3.0</v>
       </c>
       <c r="D126" s="1">
-        <v>1.0</v>
+        <v>55.0</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>35</v>
+        <v>276</v>
+      </c>
+      <c r="G126" s="1">
+        <v>4.0</v>
       </c>
       <c r="H126" s="1">
         <v>2.0</v>
+      </c>
+      <c r="I126" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="127">
@@ -4518,24 +4956,27 @@
         <v>9.0</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>277</v>
+        <v>32</v>
       </c>
       <c r="C127" s="1">
         <v>3.0</v>
       </c>
       <c r="D127" s="1">
-        <v>60.0</v>
+        <v>1.0</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>278</v>
+        <v>33</v>
       </c>
       <c r="G127" s="1">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="H127" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I127" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -4544,7 +4985,7 @@
         <v>9.0</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>180</v>
+        <v>277</v>
       </c>
       <c r="C128" s="1">
         <v>3.0</v>
@@ -4553,13 +4994,19 @@
         <v>60.0</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>181</v>
+        <v>278</v>
+      </c>
+      <c r="G128" s="1">
+        <v>6.0</v>
       </c>
       <c r="H128" s="1">
-        <v>4.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="I128" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="129">
@@ -4567,19 +5014,28 @@
         <v>9.0</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="C129" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D129" s="1">
-        <v>33.0</v>
+        <v>60.0</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>184</v>
+        <v>164</v>
+      </c>
+      <c r="G129" s="1">
+        <v>1.0</v>
       </c>
       <c r="H129" s="1">
-        <v>5.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="I129" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="130">
@@ -4587,22 +5043,25 @@
         <v>9.0</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>279</v>
+        <v>165</v>
       </c>
       <c r="C130" s="1">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D130" s="1">
-        <v>55.0</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>51</v>
+        <v>33.0</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>52</v>
+        <v>167</v>
+      </c>
+      <c r="G130" s="1">
+        <v>1.0</v>
       </c>
       <c r="H130" s="1">
-        <v>2.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="I130" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="131">
@@ -4610,22 +5069,28 @@
         <v>9.0</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C131" s="1">
         <v>3.0</v>
       </c>
       <c r="D131" s="1">
-        <v>60.0</v>
+        <v>55.0</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>268</v>
+        <v>48</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="G131" s="1">
+        <v>2.0</v>
       </c>
       <c r="H131" s="1">
-        <v>0.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="I131" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="132">
@@ -4633,22 +5098,28 @@
         <v>9.0</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>145</v>
+        <v>280</v>
       </c>
       <c r="C132" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D132" s="1">
-        <v>17.0</v>
+        <v>60.0</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>76</v>
+        <v>227</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>118</v>
+        <v>52</v>
+      </c>
+      <c r="G132" s="1">
+        <v>6.0</v>
       </c>
       <c r="H132" s="1">
-        <v>4.0</v>
+        <v>0.0</v>
+      </c>
+      <c r="I132" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="133">
@@ -4656,22 +5127,28 @@
         <v>9.0</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>267</v>
+        <v>130</v>
       </c>
       <c r="C133" s="1">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D133" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G133" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H133" s="1">
         <v>4.0</v>
       </c>
-      <c r="E133" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="H133" s="1">
-        <v>3.0</v>
+      <c r="I133" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="134">
@@ -4679,25 +5156,28 @@
         <v>9.0</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>281</v>
+        <v>226</v>
       </c>
       <c r="C134" s="1">
         <v>3.0</v>
       </c>
       <c r="D134" s="1">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="G134" s="1">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="H134" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
+      </c>
+      <c r="I134" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="135">
@@ -4705,22 +5185,28 @@
         <v>9.0</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C135" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D135" s="1">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>151</v>
+        <v>201</v>
+      </c>
+      <c r="G135" s="1">
+        <v>2.0</v>
       </c>
       <c r="H135" s="1">
-        <v>4.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="I135" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="136">
@@ -4728,25 +5214,28 @@
         <v>9.0</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C136" s="1">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D136" s="1">
-        <v>60.0</v>
+        <v>12.0</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>284</v>
+        <v>136</v>
       </c>
       <c r="G136" s="1">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H136" s="1">
-        <v>0.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="I136" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="137">
@@ -4754,7 +5243,7 @@
         <v>9.0</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C137" s="1">
         <v>3.0</v>
@@ -4763,16 +5252,19 @@
         <v>60.0</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>155</v>
+        <v>284</v>
       </c>
       <c r="G137" s="1">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="H137" s="1">
-        <v>2.0</v>
+        <v>0.0</v>
+      </c>
+      <c r="I137" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="138">
@@ -4780,7 +5272,7 @@
         <v>9.0</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C138" s="1">
         <v>3.0</v>
@@ -4789,15 +5281,18 @@
         <v>60.0</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>214</v>
+        <v>140</v>
       </c>
       <c r="G138" s="1">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="H138" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I138" s="1">
         <v>1.0</v>
       </c>
     </row>
@@ -4806,48 +5301,1388 @@
         <v>9.0</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C139" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D139" s="1">
-        <v>18.0</v>
+        <v>60.0</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>30</v>
+        <v>209</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>126</v>
+        <v>210</v>
+      </c>
+      <c r="G139" s="1">
+        <v>7.0</v>
       </c>
       <c r="H139" s="1">
-        <v>4.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="I139" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C140" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D140" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G140" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H140" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I140" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1">
         <v>11.0</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B141" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C141" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D141" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G141" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H141" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="I141" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C142" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D142" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G142" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H142" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="I142" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C143" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D143" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G143" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H143" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I143" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C144" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D144" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G144" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="H144" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I144" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C145" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D145" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G145" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H145" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="I145" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C146" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D146" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G146" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="H146" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I146" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C147" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D147" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G147" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H147" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I147" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C148" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D148" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G148" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H148" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="I148" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C149" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D149" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G149" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H149" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I149" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C150" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D150" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G150" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H150" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I150" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C151" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D151" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G151" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H151" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I151" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C152" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D152" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G152" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H152" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I152" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C153" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D153" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G153" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="H153" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I153" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C154" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D154" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G154" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H154" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="I154" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C155" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D155" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G155" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="H155" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="I155" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C156" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D156" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G156" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H156" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="I156" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C157" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D157" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G157" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H157" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I157" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C158" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D158" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G158" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H158" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="I158" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C159" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D159" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C140" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D140" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="E140" s="1" t="s">
+      <c r="F159" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G159" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H159" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I159" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C160" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D160" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G160" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H160" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I160" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C161" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D161" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G161" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H161" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I161" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C162" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D162" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F140" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G140" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="H140" s="1">
+      <c r="F162" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G162" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H162" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I162" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C163" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D163" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G163" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H163" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I163" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C164" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D164" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G164" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H164" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="I164" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C165" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D165" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G165" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="H165" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I165" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C166" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D166" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G166" s="1">
         <v>5.0</v>
+      </c>
+      <c r="H166" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="I166" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C167" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D167" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G167" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H167" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I167" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C168" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D168" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G168" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="H168" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="I168" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C169" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D169" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G169" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H169" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I169" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C170" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D170" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G170" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H170" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I170" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C171" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D171" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G171" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H171" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="I171" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C172" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D172" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G172" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H172" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I172" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C173" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D173" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G173" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H173" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I173" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C174" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D174" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G174" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H174" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I174" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C175" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D175" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G175" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H175" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="I175" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C176" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D176" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G176" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="H176" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I176" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C177" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D177" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G177" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="H177" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="I177" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C178" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D178" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G178" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H178" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I178" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C179" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D179" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G179" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H179" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I179" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C180" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D180" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G180" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H180" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I180" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C181" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D181" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G181" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="H181" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I181" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C182" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D182" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G182" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H182" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="I182" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C183" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D183" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G183" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H183" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="I183" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C184" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D184" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G184" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H184" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I184" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C185" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D185" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="G185" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="H185" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I185" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C186" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D186" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G186" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H186" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="I186" s="1">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -4871,43 +6706,43 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>23</v>
@@ -4915,7 +6750,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -4962,7 +6797,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1">
         <v>0.0</v>
@@ -5009,7 +6844,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B4" s="1">
         <v>0.0</v>
@@ -5056,7 +6891,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1">
         <v>0.0</v>
@@ -5103,7 +6938,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1">
         <v>0.0</v>
@@ -5150,7 +6985,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1">
         <v>1.0</v>
@@ -5197,7 +7032,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B8" s="1">
         <v>0.0</v>
@@ -5244,7 +7079,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B9" s="1">
         <v>0.0</v>
@@ -5291,7 +7126,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B10" s="1">
         <v>0.0</v>
@@ -5338,7 +7173,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B11" s="1">
         <v>0.0</v>
@@ -5385,7 +7220,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B12" s="1">
         <v>1.0</v>
@@ -5432,7 +7267,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B13" s="1">
         <v>0.0</v>
@@ -5479,7 +7314,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B14" s="1">
         <v>0.0</v>
@@ -5526,7 +7361,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B15" s="1">
         <v>0.0</v>
@@ -5573,7 +7408,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B16" s="1">
         <v>0.0</v>
@@ -5620,7 +7455,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B17" s="1">
         <v>0.0</v>
@@ -5667,7 +7502,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="B18" s="1">
         <v>1.0</v>
@@ -5714,7 +7549,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="B19" s="1">
         <v>0.0</v>
@@ -5761,7 +7596,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="B20" s="1">
         <v>0.0</v>
@@ -5808,7 +7643,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="B21" s="1">
         <v>0.0</v>
@@ -5855,7 +7690,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="B22" s="1">
         <v>1.0</v>
@@ -5902,7 +7737,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="B23" s="1">
         <v>0.0</v>
@@ -5949,7 +7784,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="B24" s="1">
         <v>1.0</v>
@@ -5996,7 +7831,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="B25" s="1">
         <v>1.0</v>
@@ -6043,7 +7878,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="B26" s="1">
         <v>0.0</v>
@@ -6090,7 +7925,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="B27" s="1">
         <v>0.0</v>
@@ -6137,7 +7972,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="B28" s="1">
         <v>1.0</v>
@@ -6184,7 +8019,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="B29" s="1">
         <v>0.0</v>
@@ -6231,7 +8066,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="B30" s="1">
         <v>1.0</v>
@@ -6278,7 +8113,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="B31" s="1">
         <v>0.0</v>
@@ -6325,7 +8160,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="B32" s="1">
         <v>0.0</v>
@@ -6372,7 +8207,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="B33" s="1">
         <v>0.0</v>
@@ -6419,7 +8254,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="B34" s="1">
         <v>0.0</v>
@@ -6466,7 +8301,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="B35" s="1">
         <v>0.0</v>
@@ -6513,7 +8348,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="B36" s="1">
         <v>0.0</v>
@@ -6560,7 +8395,7 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="B37" s="1">
         <v>0.0</v>
@@ -6607,7 +8442,7 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="B38" s="1">
         <v>1.0</v>
@@ -6654,7 +8489,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="B39" s="1">
         <v>0.0</v>
@@ -6701,7 +8536,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="B40" s="1">
         <v>0.0</v>
@@ -6748,7 +8583,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="B41" s="1">
         <v>1.0</v>
@@ -6795,7 +8630,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="B42" s="1">
         <v>1.0</v>
@@ -6842,7 +8677,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="B43" s="1">
         <v>0.0</v>
@@ -6889,7 +8724,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="B44" s="1">
         <v>1.0</v>
@@ -6936,7 +8771,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="B45" s="1">
         <v>0.0</v>
@@ -6983,7 +8818,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="B46" s="1">
         <v>1.0</v>
@@ -7030,7 +8865,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="B47" s="1">
         <v>0.0</v>
@@ -7077,7 +8912,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="B48" s="1">
         <v>0.0</v>
@@ -7124,7 +8959,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="B49" s="1">
         <v>0.0</v>
@@ -7171,7 +9006,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="B50" s="1">
         <v>1.0</v>
@@ -7218,7 +9053,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="B51" s="1">
         <v>1.0</v>
@@ -7265,7 +9100,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="B52" s="1">
         <v>0.0</v>
@@ -7312,7 +9147,7 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="B53" s="1">
         <v>0.0</v>
